--- a/artfynd/A 35341-2026 artfynd.xlsx
+++ b/artfynd/A 35341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042889</v>
       </c>
       <c r="B2" t="n">
-        <v>93355</v>
+        <v>93356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042890</v>
       </c>
       <c r="B3" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35341-2026 artfynd.xlsx
+++ b/artfynd/A 35341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042889</v>
       </c>
       <c r="B2" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042890</v>
       </c>
       <c r="B3" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136042888</v>
       </c>
       <c r="B4" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35341-2026 artfynd.xlsx
+++ b/artfynd/A 35341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042889</v>
       </c>
       <c r="B2" t="n">
-        <v>93357</v>
+        <v>93363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042890</v>
       </c>
       <c r="B3" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136042888</v>
       </c>
       <c r="B4" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35341-2026 artfynd.xlsx
+++ b/artfynd/A 35341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042889</v>
       </c>
       <c r="B2" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042890</v>
       </c>
       <c r="B3" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136042888</v>
       </c>
       <c r="B4" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
